--- a/data/trans_bre/DCD-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 15,41</t>
+          <t>8,39; 15,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 12,61</t>
+          <t>5,45; 12,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,04; 21,88</t>
+          <t>13,61; 22,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,68; 145,04</t>
+          <t>58,09; 137,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,74; 120,61</t>
+          <t>38,5; 117,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,67; 96,61</t>
+          <t>47,71; 96,55</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 9,04</t>
+          <t>5,16; 9,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,11</t>
+          <t>3,55; 7,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,58</t>
+          <t>4,02; 13,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,27; 211,26</t>
+          <t>88,62; 214,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,91; 155,61</t>
+          <t>58,11; 155,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,15; 163,55</t>
+          <t>40,12; 160,17</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,35</t>
+          <t>4,43; 11,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,45</t>
+          <t>-0,66; 5,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,31</t>
+          <t>8,01; 14,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122,15; 864,89</t>
+          <t>111,9; 883,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 164,92</t>
+          <t>-12,66; 171,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,7; 238,54</t>
+          <t>81,52; 229,86</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,02</t>
+          <t>8,13; 11,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,93</t>
+          <t>4,85; 7,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,05</t>
+          <t>8,11; 15,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109,62; 180,64</t>
+          <t>110,32; 189,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,93; 126,48</t>
+          <t>65,8; 129,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,82; 148,98</t>
+          <t>65,78; 150,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DCD-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,66</t>
+          <t>18,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,07</t>
+          <t>8,84; 15,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,61</t>
+          <t>5,37; 12,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,61; 22,09</t>
+          <t>13,89; 22,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,09; 137,23</t>
+          <t>61,84; 144,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,5; 117,99</t>
+          <t>37,58; 119,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,71; 96,55</t>
+          <t>49,66; 101,08</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>11,25</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,12</t>
+          <t>5,34; 9,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,05</t>
+          <t>3,62; 7,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 13,4</t>
+          <t>9,23; 13,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,62; 214,7</t>
+          <t>94,44; 218,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,11; 155,96</t>
+          <t>61,45; 155,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,12; 160,17</t>
+          <t>74,4; 129,82</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>12,28</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>146,46%</t>
+          <t>155,16%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,06</t>
+          <t>4,22; 10,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,4</t>
+          <t>-0,37; 5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 14,91</t>
+          <t>8,89; 15,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111,9; 883,6</t>
+          <t>111,56; 822,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 171,07</t>
+          <t>-7,05; 171,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,52; 229,86</t>
+          <t>91,7; 252,43</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100,23%</t>
+          <t>106,86%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,33</t>
+          <t>8,03; 11,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,93</t>
+          <t>4,85; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,27</t>
+          <t>12,1; 15,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110,32; 189,99</t>
+          <t>109,67; 184,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 129,27</t>
+          <t>64,12; 128,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,78; 150,27</t>
+          <t>86,48; 128,87</t>
         </is>
       </c>
     </row>
